--- a/experiments/sentence_focus/experiment_code/State Change Followup Materials.xlsx
+++ b/experiments/sentence_focus/experiment_code/State Change Followup Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bowdoin-my.sharepoint.com/personal/c_hambric_bowdoin_edu/Documents/Documents/object-state-changes/experiments/sentence_focus/experiment_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="8_{D7A1A05E-A6AF-48FA-B7EE-E5C7DCBCF7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E4460DC-1425-480C-B8FB-0693FF62FB83}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="8_{D7A1A05E-A6AF-48FA-B7EE-E5C7DCBCF7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD868692-A821-4A80-AA04-EB327A7462EE}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="26340" windowHeight="13815" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -2040,7 +2040,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2068,11 +2068,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4999,19 +4994,19 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+      <c r="A43" s="4">
         <v>41</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/napkin.jpg</v>
       </c>
@@ -6006,19 +6001,19 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E62" s="17" t="str">
+      <c r="E62" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/comb.jpg</v>
       </c>
@@ -6218,19 +6213,19 @@
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+      <c r="A66" s="4">
         <v>64</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E66" s="17" t="str">
+      <c r="E66" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/hairclip.jpg</v>
       </c>
@@ -7437,19 +7432,19 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E89" s="17" t="str">
+      <c r="E89" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/frisbee.jpg</v>
       </c>
@@ -10882,7 +10877,7 @@
     <col min="4" max="4" width="15.75" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
     <col min="8" max="8" width="10.625" customWidth="1"/>
     <col min="9" max="9" width="17.125" customWidth="1"/>
     <col min="10" max="10" width="43.375" customWidth="1"/>
@@ -13098,55 +13093,55 @@
         <v>&lt;p style='font-size:30px;color: #508AB0;'&gt;Was a car mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
         <v>41</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/napkin.jpg</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="H43" s="17">
+      <c r="H43" s="4">
         <v>1</v>
       </c>
-      <c r="I43" s="17" t="str">
+      <c r="I43" s="4" t="str">
         <f t="shared" si="1"/>
         <v>&lt;p style='font-size:36px;'&gt;A fork is on the napkin.&lt;/p&gt;</v>
       </c>
-      <c r="J43" s="17" t="str">
+      <c r="J43" s="4" t="str">
         <f t="shared" ref="J43:K43" si="49">CONCATENATE("Was ",L43, " mentioned in the previous sentence?")</f>
         <v>Was a panda mentioned in the previous sentence?</v>
       </c>
-      <c r="K43" s="17" t="str">
+      <c r="K43" s="4" t="str">
         <f t="shared" si="49"/>
         <v>Was a fork mentioned in the previous sentence?</v>
       </c>
-      <c r="L43" s="17" t="s">
+      <c r="L43" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="M43" s="17" t="s">
+      <c r="M43" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="N43" s="17" t="str">
+      <c r="N43" s="4" t="str">
         <f t="shared" si="3"/>
         <v>&lt;p style='font-size:30px; color: #508AB0; '&gt;Was a fork mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
-      <c r="O43" s="17" t="str">
+      <c r="O43" s="4" t="str">
         <f t="shared" si="4"/>
         <v>&lt;p style='font-size:30px;color: #508AB0;'&gt;Was a panda mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
@@ -14116,55 +14111,55 @@
         <v>&lt;p style='font-size:30px;color: #508AB0;'&gt;Was fruit mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="62" spans="1:26" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E62" s="17" t="str">
+      <c r="E62" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/comb.jpg</v>
       </c>
-      <c r="F62" s="18" t="s">
+      <c r="F62" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="G62" s="17" t="s">
+      <c r="G62" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="H62" s="17">
+      <c r="H62" s="4">
         <v>1</v>
       </c>
-      <c r="I62" s="17" t="str">
+      <c r="I62" s="4" t="str">
         <f t="shared" si="1"/>
         <v>&lt;p style='font-size:36px;'&gt;A needle is on the mouse pad.&lt;/p&gt;</v>
       </c>
-      <c r="J62" s="17" t="str">
+      <c r="J62" s="4" t="str">
         <f t="shared" ref="J62:K62" si="68">CONCATENATE("Was ",L62, " mentioned in the previous sentence?")</f>
         <v>Was a meadow mentioned in the previous sentence?</v>
       </c>
-      <c r="K62" s="17" t="str">
+      <c r="K62" s="4" t="str">
         <f t="shared" si="68"/>
         <v>Was a mouse pad mentioned in the previous sentence?</v>
       </c>
-      <c r="L62" s="17" t="s">
+      <c r="L62" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="M62" s="17" t="s">
+      <c r="M62" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="N62" s="17" t="str">
+      <c r="N62" s="4" t="str">
         <f t="shared" si="3"/>
         <v>&lt;p style='font-size:30px; color: #508AB0; '&gt;Was a mouse pad mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
-      <c r="O62" s="17" t="str">
+      <c r="O62" s="4" t="str">
         <f t="shared" si="4"/>
         <v>&lt;p style='font-size:30px;color: #508AB0;'&gt;Was a meadow mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
@@ -14328,55 +14323,55 @@
         <v>&lt;p style='font-size:30px;color: #508AB0;'&gt;Was a dinosaur mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="66" spans="1:26" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
         <v>64</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E66" s="17" t="str">
+      <c r="E66" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/hairclip.jpg</v>
       </c>
-      <c r="F66" s="18" t="s">
+      <c r="F66" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="G66" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="H66" s="17">
+      <c r="H66" s="4">
         <v>1</v>
       </c>
-      <c r="I66" s="17" t="str">
+      <c r="I66" s="4" t="str">
         <f t="shared" si="1"/>
         <v>&lt;p style='font-size:36px;'&gt;A man is boiling potatoes.&lt;/p&gt;</v>
       </c>
-      <c r="J66" s="17" t="str">
+      <c r="J66" s="4" t="str">
         <f t="shared" ref="J66:K66" si="72">CONCATENATE("Was ",L66, " mentioned in the previous sentence?")</f>
         <v>Was a rat mentioned in the previous sentence?</v>
       </c>
-      <c r="K66" s="17" t="str">
+      <c r="K66" s="4" t="str">
         <f t="shared" si="72"/>
         <v>Was a man mentioned in the previous sentence?</v>
       </c>
-      <c r="L66" s="17" t="s">
+      <c r="L66" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="M66" s="17" t="s">
+      <c r="M66" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="N66" s="17" t="str">
+      <c r="N66" s="4" t="str">
         <f t="shared" si="3"/>
         <v>&lt;p style='font-size:30px; color: #508AB0; '&gt;Was a man mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
-      <c r="O66" s="17" t="str">
+      <c r="O66" s="4" t="str">
         <f t="shared" si="4"/>
         <v>&lt;p style='font-size:30px;color: #508AB0;'&gt;Was a rat mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
@@ -15558,55 +15553,55 @@
         <v>&lt;p style='font-size:30px;color: #508AB0;'&gt;Was making waffles mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+    <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E89" s="17" t="str">
+      <c r="E89" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/frisbee.jpg</v>
       </c>
-      <c r="F89" s="18" t="s">
+      <c r="F89" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="G89" s="17" t="s">
+      <c r="G89" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="H89" s="17">
+      <c r="H89" s="4">
         <v>1</v>
       </c>
-      <c r="I89" s="17" t="str">
+      <c r="I89" s="4" t="str">
         <f t="shared" si="1"/>
         <v>&lt;p style='font-size:36px;'&gt;A man is playing with a cat.&lt;/p&gt;</v>
       </c>
-      <c r="J89" s="17" t="str">
+      <c r="J89" s="4" t="str">
         <f t="shared" ref="J89:K89" si="95">CONCATENATE("Was ",L89, " mentioned in the previous sentence?")</f>
         <v>Was walking in the rain mentioned in the previous sentence?</v>
       </c>
-      <c r="K89" s="17" t="str">
+      <c r="K89" s="4" t="str">
         <f t="shared" si="95"/>
         <v>Was playing with a cat mentioned in the previous sentence?</v>
       </c>
-      <c r="L89" s="17" t="s">
+      <c r="L89" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="M89" s="17" t="s">
+      <c r="M89" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="N89" s="17" t="str">
+      <c r="N89" s="4" t="str">
         <f t="shared" si="3"/>
         <v>&lt;p style='font-size:30px; color: #508AB0; '&gt;Was playing with a cat mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
-      <c r="O89" s="17" t="str">
+      <c r="O89" s="4" t="str">
         <f t="shared" si="4"/>
         <v>&lt;p style='font-size:30px;color: #508AB0;'&gt;Was walking in the rain mentioned in the previous sentence?&lt;/p&gt;</v>
       </c>
@@ -18775,19 +18770,19 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+      <c r="A43" s="4">
         <v>41</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/napkin.jpg</v>
       </c>
@@ -19782,19 +19777,19 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E62" s="17" t="str">
+      <c r="E62" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/comb.jpg</v>
       </c>
@@ -19994,19 +19989,19 @@
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+      <c r="A66" s="4">
         <v>64</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E66" s="17" t="str">
+      <c r="E66" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/hairclip.jpg</v>
       </c>
@@ -21213,19 +21208,19 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E89" s="17" t="str">
+      <c r="E89" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/frisbee.jpg</v>
       </c>
@@ -24417,19 +24412,19 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+      <c r="A43" s="4">
         <v>41</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/napkin.jpg</v>
       </c>
@@ -25424,19 +25419,19 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E62" s="17" t="str">
+      <c r="E62" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/comb.jpg</v>
       </c>
@@ -25636,19 +25631,19 @@
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+      <c r="A66" s="4">
         <v>64</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E66" s="17" t="str">
+      <c r="E66" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/hairclip.jpg</v>
       </c>
@@ -26855,19 +26850,19 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E89" s="17" t="str">
+      <c r="E89" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/frisbee.jpg</v>
       </c>
@@ -30063,19 +30058,19 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+      <c r="A43" s="4">
         <v>41</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/napkin.jpg</v>
       </c>
@@ -31070,19 +31065,19 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E62" s="17" t="str">
+      <c r="E62" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/comb.jpg</v>
       </c>
@@ -31282,19 +31277,19 @@
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+      <c r="A66" s="4">
         <v>64</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E66" s="17" t="str">
+      <c r="E66" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/hairclip.jpg</v>
       </c>
@@ -32501,19 +32496,19 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E89" s="17" t="str">
+      <c r="E89" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/frisbee.jpg</v>
       </c>
@@ -33495,7 +33490,7 @@
     <col min="3" max="4" width="10.625" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
-    <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="26" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -35704,19 +35699,19 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+      <c r="A43" s="4">
         <v>41</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/napkin.jpg</v>
       </c>
@@ -36711,19 +36706,19 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E62" s="17" t="str">
+      <c r="E62" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/comb.jpg</v>
       </c>
@@ -36923,19 +36918,19 @@
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+      <c r="A66" s="4">
         <v>64</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E66" s="17" t="str">
+      <c r="E66" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/hairclip.jpg</v>
       </c>
@@ -38142,19 +38137,19 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E89" s="17" t="str">
+      <c r="E89" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/frisbee.jpg</v>
       </c>
@@ -39140,7 +39135,7 @@
     <col min="3" max="4" width="10.625" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
-    <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
     <col min="8" max="26" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -41349,19 +41344,19 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+      <c r="A43" s="4">
         <v>41</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/napkin.jpg</v>
       </c>
@@ -42356,19 +42351,19 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E62" s="17" t="str">
+      <c r="E62" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/comb.jpg</v>
       </c>
@@ -42568,19 +42563,19 @@
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+      <c r="A66" s="4">
         <v>64</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E66" s="17" t="str">
+      <c r="E66" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/hairclip.jpg</v>
       </c>
@@ -43787,19 +43782,19 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E89" s="17" t="str">
+      <c r="E89" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/frisbee.jpg</v>
       </c>
@@ -44775,6 +44770,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:O1016"/>
   <sheetFormatPr defaultColWidth="16.875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="43.75" customWidth="1"/>
+    <col min="7" max="7" width="25.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
@@ -46981,19 +46980,19 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
+      <c r="A43" s="4">
         <v>41</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/napkin.jpg</v>
       </c>
@@ -47988,19 +47987,19 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E62" s="17" t="str">
+      <c r="E62" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/comb.jpg</v>
       </c>
@@ -48200,19 +48199,19 @@
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
+      <c r="A66" s="4">
         <v>64</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E66" s="17" t="str">
+      <c r="E66" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/hairclip.jpg</v>
       </c>
@@ -49419,19 +49418,19 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E89" s="17" t="str">
+      <c r="E89" s="4" t="str">
         <f t="shared" si="47"/>
         <v>PICTURES/frisbee.jpg</v>
       </c>
